--- a/InputData/fuels/FoVTStCT/Fraction of Vehicle Types Subject to Carbon Tax.xlsx
+++ b/InputData/fuels/FoVTStCT/Fraction of Vehicle Types Subject to Carbon Tax.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\U.S. Models\eps-us\InputData\fuels\FoVTStCT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\fuels\FoVTStCT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5736511-220B-437D-B4AB-6A25C04B2BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD98330-8F7F-42FA-A183-BC7936D521E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30495" yWindow="1140" windowWidth="23445" windowHeight="14565" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
+    <workbookView xWindow="2450" yWindow="1380" windowWidth="13530" windowHeight="10720" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="BFoVTStCT" sheetId="3" r:id="rId2"/>
+    <sheet name="FoVTStCT" sheetId="3" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -94,13 +94,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -108,7 +108,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -116,7 +116,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -125,6 +125,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="161"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,15 +159,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6E9FC10A-7EC7-456E-8CAE-AFD069EE3505}"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -376,7 +383,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -672,38 +679,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE5FEEC-01CE-4291-999E-35B30A1256CF}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -711,18 +720,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472BA136-BC62-4073-9A64-988FF7A4A244}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AE28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="46.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="46.25" customWidth="1"/>
+    <col min="2" max="2" width="10.25" customWidth="1"/>
+    <col min="3" max="3" width="10.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -817,7 +826,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -912,7 +921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1007,7 +1016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1102,7 +1111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1197,7 +1206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1292,7 +1301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1387,7 +1396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -1419,7 +1428,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1451,7 +1460,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1483,7 +1492,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1515,7 +1524,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1547,7 +1556,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1579,7 +1588,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1611,7 +1620,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1643,7 +1652,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -1675,7 +1684,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
     </row>
-    <row r="17" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -1707,7 +1716,7 @@
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
     </row>
-    <row r="18" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -1739,7 +1748,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
     </row>
-    <row r="19" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -1771,7 +1780,7 @@
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
     </row>
-    <row r="20" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1803,7 +1812,7 @@
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
     </row>
-    <row r="21" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1835,7 +1844,7 @@
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
     </row>
-    <row r="22" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1867,7 +1876,7 @@
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
     </row>
-    <row r="23" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1899,7 +1908,7 @@
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
     </row>
-    <row r="24" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1931,7 +1940,7 @@
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
     </row>
-    <row r="25" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1963,7 +1972,7 @@
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
     </row>
-    <row r="26" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1995,11 +2004,183 @@
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
     </row>
-    <row r="28" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFC71EE5-8448-4557-9280-14C8C23F2E0D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2485FB8A-08EF-4245-A3CC-46D1AF4D31D3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB02EECC-6BD0-4617-AA03-1A894AB79206}"/>
 </file>